--- a/Results/Two_Datasets_Assessment/Mushroom/Tables/overall_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Mushroom/Tables/overall_scores.xlsx
@@ -491,13 +491,13 @@
         <v>0.6854540568620545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1712066308380989</v>
+        <v>0.2468983155019921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8740643163992137</v>
+        <v>0.6501790175485291</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5877629069160155</v>
+        <v>0.5433048226599781</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.377432168857154</v>
+        <v>0.3666729230935759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4593039257982813</v>
+        <v>0.5099445363163269</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5965175288041394</v>
+        <v>0.7325289107288828</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4677193039235878</v>
+        <v>0.5194112033509932</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -547,23 +547,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3666729230935759</v>
+        <v>0.377432168857154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4039431302146414</v>
+        <v>0.5483620331151577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6238393249874938</v>
+        <v>0.5651465293055633</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4550039057980709</v>
+        <v>0.4850254362690779</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -580,23 +580,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CopulaGAN</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5100138975778759</v>
+        <v>0.3997825632837796</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2754930305176135</v>
+        <v>0.4937338788414433</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5520664642022749</v>
+        <v>0.580711160887031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4522734074471169</v>
+        <v>0.4822465372320541</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -613,23 +613,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3363148782492614</v>
+        <v>0.5100138975778759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.343779489884602</v>
+        <v>0.2864860607661532</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4949530413496791</v>
+        <v>0.5187481196936311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3861457106699889</v>
+        <v>0.4455758131690857</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -637,7 +637,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -646,23 +646,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CopulaGAN</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3997825632837796</v>
+        <v>0.2212644916550226</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3137404995245627</v>
+        <v>0.5100652890254719</v>
       </c>
       <c r="G7" t="n">
-        <v>0.425874725649952</v>
+        <v>0.6793990320601035</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3817975928658662</v>
+        <v>0.4453450929876817</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -670,7 +670,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2212644916550226</v>
+        <v>0.3363148782492614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3697079075243822</v>
+        <v>0.4824131139296354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5898036904498916</v>
+        <v>0.542977064252405</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3763592760542912</v>
+        <v>0.4421430047543167</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -722,13 +722,13 @@
         <v>0.1717628035644512</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5327151221325226</v>
+        <v>0.4794436099192703</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25</v>
+        <v>0.2294567983077689</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3035196580655373</v>
+        <v>0.2813752438938922</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
